--- a/Fase 2/SIGMA_Burndown_Burnup.xlsx
+++ b/Fase 2/SIGMA_Burndown_Burnup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\SIGMA\Fase 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D211B74-D243-4669-9133-252E114A5D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9725D6-50AF-4EA9-BC2D-FA974C5D2531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
@@ -317,7 +317,7 @@
     <t>Sprint 3 · Burndown y Burnup</t>
   </si>
   <si>
-    <t>Recursos y recurrencia · del 30-09-2026 al 13-10-2026 · 23 historias · 118 puntos comprometidos · 9 días hábiles</t>
+    <t>Recursos y recurrencia · del 30-09-2026 al 13-10-2026 · 23 historias · 118 puntos comprometidos · 9 días hábiles  ·  Alcance ampliado en 34 pts no planificados (HU-059, HU-066, HU-067, HU-068, HU-069, HU-077)</t>
   </si>
   <si>
     <t>Sprint 4 · Burndown y Burnup</t>
@@ -650,23 +650,23 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,8 +831,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -946,7 +946,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0B61-48CE-88D7-E098F23F8861}"/>
+              <c16:uniqueId val="{00000000-B132-4762-B645-021A0F2657D1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -990,8 +990,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -1105,7 +1105,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0B61-48CE-88D7-E098F23F8861}"/>
+              <c16:uniqueId val="{00000001-B132-4762-B645-021A0F2657D1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1431,8 +1431,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -1546,7 +1546,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E325-4C89-A114-043BA54C6D71}"/>
+              <c16:uniqueId val="{00000000-EC1D-4FCC-8371-492022CFF2E3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1581,8 +1581,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -1696,7 +1696,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E325-4C89-A114-043BA54C6D71}"/>
+              <c16:uniqueId val="{00000001-EC1D-4FCC-8371-492022CFF2E3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2013,8 +2013,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -2128,7 +2128,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7C90-40B7-847E-2007F24E3CE4}"/>
+              <c16:uniqueId val="{00000000-FEEB-40E5-9A79-4E20A3027062}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2172,8 +2172,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -2287,7 +2287,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7C90-40B7-847E-2007F24E3CE4}"/>
+              <c16:uniqueId val="{00000001-FEEB-40E5-9A79-4E20A3027062}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2613,8 +2613,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -2728,7 +2728,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-465D-4414-9317-7BCD47C51F1B}"/>
+              <c16:uniqueId val="{00000000-166E-4F7D-9AFC-5722D9B2A42E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2763,8 +2763,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -2878,7 +2878,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-465D-4414-9317-7BCD47C51F1B}"/>
+              <c16:uniqueId val="{00000001-166E-4F7D-9AFC-5722D9B2A42E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3195,8 +3195,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -3285,7 +3285,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-606A-470C-81EC-FCF112EDC922}"/>
+              <c16:uniqueId val="{00000000-8FEB-43CE-BD95-2FDECDAB0C88}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3329,8 +3329,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -3419,7 +3419,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-606A-470C-81EC-FCF112EDC922}"/>
+              <c16:uniqueId val="{00000001-8FEB-43CE-BD95-2FDECDAB0C88}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3744,8 +3744,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -3834,7 +3834,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-84B5-44FF-931B-D947B33A202D}"/>
+              <c16:uniqueId val="{00000000-5BC3-4248-A6E2-7C7B08511935}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3869,8 +3869,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -3959,7 +3959,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-84B5-44FF-931B-D947B33A202D}"/>
+              <c16:uniqueId val="{00000001-5BC3-4248-A6E2-7C7B08511935}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4286,8 +4286,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -4401,7 +4401,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3F78-475A-87ED-4A1299CC6F66}"/>
+              <c16:uniqueId val="{00000000-9D41-4760-BC7C-E2BCC26D4EB9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4436,8 +4436,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -4551,7 +4551,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3F78-475A-87ED-4A1299CC6F66}"/>
+              <c16:uniqueId val="{00000001-9D41-4760-BC7C-E2BCC26D4EB9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4868,8 +4868,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -4977,7 +4977,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D20A-4B85-A77D-2DF19AD7A487}"/>
+              <c16:uniqueId val="{00000000-172D-46DF-BB90-EFEEF28ECA74}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5021,8 +5021,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -5130,7 +5130,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D20A-4B85-A77D-2DF19AD7A487}"/>
+              <c16:uniqueId val="{00000001-172D-46DF-BB90-EFEEF28ECA74}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5456,8 +5456,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -5565,7 +5565,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7B55-4580-A947-1D85D4E4F16C}"/>
+              <c16:uniqueId val="{00000000-91CC-401B-8B02-5B7B1E06DF15}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5600,8 +5600,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -5709,7 +5709,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7B55-4580-A947-1D85D4E4F16C}"/>
+              <c16:uniqueId val="{00000001-91CC-401B-8B02-5B7B1E06DF15}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6026,8 +6026,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -6100,31 +6100,31 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>104.9</c:v>
+                  <c:v>135.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91.8</c:v>
+                  <c:v>118.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>78.7</c:v>
+                  <c:v>101.3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65.599999999999994</c:v>
+                  <c:v>84.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>52.4</c:v>
+                  <c:v>67.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>39.299999999999997</c:v>
+                  <c:v>50.7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>26.2</c:v>
+                  <c:v>33.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13.1</c:v>
+                  <c:v>16.899999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6135,7 +6135,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DD78-47B1-95C2-9C229019F147}"/>
+              <c16:uniqueId val="{00000000-90F3-45C0-86C9-8423F7431A84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6179,8 +6179,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -6253,34 +6253,34 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6288,7 +6288,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DD78-47B1-95C2-9C229019F147}"/>
+              <c16:uniqueId val="{00000001-90F3-45C0-86C9-8423F7431A84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6614,8 +6614,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -6723,7 +6723,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B9A5-4DCF-9F68-AE262082C043}"/>
+              <c16:uniqueId val="{00000000-5F19-4FE3-B914-D00D105EF2E8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6758,8 +6758,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -6832,34 +6832,34 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>118</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6867,7 +6867,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B9A5-4DCF-9F68-AE262082C043}"/>
+              <c16:uniqueId val="{00000001-5F19-4FE3-B914-D00D105EF2E8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7184,8 +7184,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -7299,7 +7299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8F9A-444C-AD96-4AB740AA9F18}"/>
+              <c16:uniqueId val="{00000000-8CAE-46D0-AE60-2209B4ACED66}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7343,8 +7343,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -7458,7 +7458,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8F9A-444C-AD96-4AB740AA9F18}"/>
+              <c16:uniqueId val="{00000001-8CAE-46D0-AE60-2209B4ACED66}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7784,8 +7784,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -7899,7 +7899,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-51F8-48CE-B8B1-882D75396204}"/>
+              <c16:uniqueId val="{00000000-F856-43EA-9790-3D37FCC22436}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7934,8 +7934,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -8049,7 +8049,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-51F8-48CE-B8B1-882D75396204}"/>
+              <c16:uniqueId val="{00000001-F856-43EA-9790-3D37FCC22436}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8366,8 +8366,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -8481,7 +8481,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EE12-43E7-98B5-D2391230AE40}"/>
+              <c16:uniqueId val="{00000000-4CEF-4B47-95A0-1B9E35DE508D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8525,8 +8525,8 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
@@ -8640,7 +8640,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EE12-43E7-98B5-D2391230AE40}"/>
+              <c16:uniqueId val="{00000001-4CEF-4B47-95A0-1B9E35DE508D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9650,7 +9650,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B6:I42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -9658,27 +9658,27 @@
     <col min="4" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>4</v>
       </c>
@@ -9692,7 +9692,7 @@
       <c r="H11" s="34"/>
       <c r="I11" s="34"/>
     </row>
-    <row r="12" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
@@ -9706,7 +9706,7 @@
       <c r="H12" s="34"/>
       <c r="I12" s="34"/>
     </row>
-    <row r="13" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
@@ -9720,7 +9720,7 @@
       <c r="H13" s="34"/>
       <c r="I13" s="34"/>
     </row>
-    <row r="14" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
@@ -9734,7 +9734,7 @@
       <c r="H14" s="34"/>
       <c r="I14" s="34"/>
     </row>
-    <row r="15" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>12</v>
       </c>
@@ -9748,7 +9748,7 @@
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
     </row>
-    <row r="16" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>14</v>
       </c>
@@ -9762,7 +9762,7 @@
       <c r="H16" s="34"/>
       <c r="I16" s="34"/>
     </row>
-    <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>16</v>
       </c>
@@ -9776,12 +9776,12 @@
       <c r="H17" s="34"/>
       <c r="I17" s="34"/>
     </row>
-    <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>19</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="7">
         <f>Release!$E$12</f>
         <v>751</v>
@@ -9827,12 +9827,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
         <v>26</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="11" t="s">
         <v>33</v>
       </c>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>35</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="11" t="s">
         <v>37</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>39</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="11" t="s">
         <v>41</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>43</v>
       </c>
@@ -10011,7 +10011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
         <v>45</v>
       </c>
@@ -10037,12 +10037,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="10" t="s">
         <v>47</v>
       </c>
@@ -10053,72 +10053,72 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
         <v>50</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="37"/>
-    </row>
-    <row r="36" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="38"/>
+    </row>
+    <row r="36" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="16" t="s">
         <v>53</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="D36" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="37"/>
-    </row>
-    <row r="37" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="38"/>
+    </row>
+    <row r="37" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="37"/>
-    </row>
-    <row r="38" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="38"/>
+    </row>
+    <row r="38" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="16" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="37"/>
-    </row>
-    <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="39" t="s">
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="38"/>
+    </row>
+    <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="35" t="s">
         <v>62</v>
       </c>
       <c r="C40" s="34"/>
@@ -10129,7 +10129,7 @@
       <c r="H40" s="34"/>
       <c r="I40" s="34"/>
     </row>
-    <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="34"/>
       <c r="C41" s="34"/>
       <c r="D41" s="34"/>
@@ -10139,7 +10139,7 @@
       <c r="H41" s="34"/>
       <c r="I41" s="34"/>
     </row>
-    <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="34"/>
       <c r="C42" s="34"/>
       <c r="D42" s="34"/>
@@ -10151,10 +10151,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B40:I42"/>
-    <mergeCell ref="D38:I38"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="D37:I37"/>
     <mergeCell ref="C11:I11"/>
     <mergeCell ref="C12:I12"/>
     <mergeCell ref="D35:I35"/>
@@ -10163,6 +10159,10 @@
     <mergeCell ref="C15:I15"/>
     <mergeCell ref="C14:I14"/>
     <mergeCell ref="C13:I13"/>
+    <mergeCell ref="B40:I42"/>
+    <mergeCell ref="D38:I38"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="D37:I37"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -10179,7 +10179,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -10193,8 +10193,8 @@
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="34"/>
@@ -10205,8 +10205,8 @@
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>64</v>
       </c>
       <c r="B2" s="34"/>
@@ -10217,7 +10217,7 @@
       <c r="G2" s="34"/>
       <c r="H2" s="34"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>65</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>67</v>
       </c>
@@ -10262,7 +10262,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>0</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>1</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>2</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>3</v>
       </c>
@@ -10390,7 +10390,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>4</v>
       </c>
@@ -10422,7 +10422,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>6</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>7</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>8</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>9</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>10</v>
       </c>
@@ -10614,7 +10614,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19" t="s">
@@ -10629,12 +10629,12 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
         <v>20</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>21</v>
       </c>
@@ -10654,7 +10654,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40" t="s">
         <v>31</v>
       </c>
@@ -10664,7 +10664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
         <v>83</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="40" t="s">
         <v>84</v>
       </c>
@@ -10684,8 +10684,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="39" t="s">
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="35" t="s">
         <v>85</v>
       </c>
       <c r="B27" s="34"/>
@@ -10696,7 +10696,7 @@
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -10706,13 +10706,13 @@
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="32" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="42" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="43" t="s">
         <v>87</v>
       </c>
       <c r="B32" s="34"/>
@@ -10723,7 +10723,7 @@
       <c r="G32" s="34"/>
       <c r="H32" s="34"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="34"/>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -10733,7 +10733,7 @@
       <c r="G33" s="34"/>
       <c r="H33" s="34"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="34"/>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -10745,10 +10745,6 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A32:H34"/>
@@ -10756,6 +10752,10 @@
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:H28"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -10772,7 +10772,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -10786,8 +10786,8 @@
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>88</v>
       </c>
       <c r="B1" s="34"/>
@@ -10798,8 +10798,8 @@
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>89</v>
       </c>
       <c r="B2" s="34"/>
@@ -10810,7 +10810,7 @@
       <c r="G2" s="34"/>
       <c r="H2" s="34"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>65</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>67</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>0</v>
       </c>
@@ -10887,7 +10887,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>1</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>2</v>
       </c>
@@ -10951,7 +10951,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>3</v>
       </c>
@@ -10983,7 +10983,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>4</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
@@ -11047,7 +11047,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>6</v>
       </c>
@@ -11079,7 +11079,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>7</v>
       </c>
@@ -11111,7 +11111,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>8</v>
       </c>
@@ -11143,7 +11143,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>9</v>
       </c>
@@ -11175,7 +11175,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19"/>
       <c r="B17" s="19"/>
       <c r="C17" s="19" t="s">
@@ -11190,12 +11190,12 @@
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40" t="s">
         <v>20</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
         <v>21</v>
       </c>
@@ -11215,7 +11215,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>31</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40" t="s">
         <v>83</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
         <v>84</v>
       </c>
@@ -11245,8 +11245,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="39" t="s">
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="35" t="s">
         <v>85</v>
       </c>
       <c r="B26" s="34"/>
@@ -11257,7 +11257,7 @@
       <c r="G26" s="34"/>
       <c r="H26" s="34"/>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="34"/>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -11269,16 +11269,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A26:H27"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -11295,7 +11295,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -11309,8 +11309,8 @@
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="34"/>
@@ -11321,8 +11321,8 @@
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>91</v>
       </c>
       <c r="B2" s="34"/>
@@ -11333,13 +11333,13 @@
       <c r="G2" s="34"/>
       <c r="H2" s="34"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>65</v>
       </c>
       <c r="B4" s="34"/>
       <c r="C4" s="23">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="D4" s="40" t="s">
         <v>66</v>
@@ -11349,7 +11349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>67</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>0</v>
       </c>
@@ -11395,11 +11395,11 @@
       </c>
       <c r="F7" s="13">
         <f t="shared" ref="F7:F16" si="0">$C$4-$E7</f>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G7" s="13">
         <f>ROUND($C$4*(1-0/$F$4),1)</f>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" ref="H7:H16" si="1">$F7-$G7</f>
@@ -11407,10 +11407,10 @@
       </c>
       <c r="K7" s="26">
         <f t="shared" ref="K7:K16" si="2">$C$4</f>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>1</v>
       </c>
@@ -11427,22 +11427,22 @@
       </c>
       <c r="F8" s="17">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G8" s="17">
         <f>ROUND($C$4*(1-1/$F$4),1)</f>
-        <v>104.9</v>
+        <v>135.1</v>
       </c>
       <c r="H8" s="17">
         <f t="shared" si="1"/>
-        <v>13.099999999999994</v>
+        <v>16.900000000000006</v>
       </c>
       <c r="K8" s="26">
         <f t="shared" si="2"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>2</v>
       </c>
@@ -11459,22 +11459,22 @@
       </c>
       <c r="F9" s="13">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G9" s="13">
         <f>ROUND($C$4*(1-2/$F$4),1)</f>
-        <v>91.8</v>
+        <v>118.2</v>
       </c>
       <c r="H9" s="13">
         <f t="shared" si="1"/>
-        <v>26.200000000000003</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="K9" s="26">
         <f t="shared" si="2"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>3</v>
       </c>
@@ -11491,22 +11491,22 @@
       </c>
       <c r="F10" s="17">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G10" s="17">
         <f>ROUND($C$4*(1-3/$F$4),1)</f>
-        <v>78.7</v>
+        <v>101.3</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>39.299999999999997</v>
+        <v>50.7</v>
       </c>
       <c r="K10" s="26">
         <f t="shared" si="2"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>4</v>
       </c>
@@ -11523,22 +11523,22 @@
       </c>
       <c r="F11" s="13">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G11" s="13">
         <f>ROUND($C$4*(1-4/$F$4),1)</f>
-        <v>65.599999999999994</v>
+        <v>84.4</v>
       </c>
       <c r="H11" s="13">
         <f t="shared" si="1"/>
-        <v>52.400000000000006</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="K11" s="26">
         <f t="shared" si="2"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
@@ -11555,22 +11555,22 @@
       </c>
       <c r="F12" s="17">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G12" s="17">
         <f>ROUND($C$4*(1-5/$F$4),1)</f>
-        <v>52.4</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" si="1"/>
-        <v>65.599999999999994</v>
+        <v>84.4</v>
       </c>
       <c r="K12" s="26">
         <f t="shared" si="2"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>6</v>
       </c>
@@ -11587,22 +11587,22 @@
       </c>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G13" s="13">
         <f>ROUND($C$4*(1-6/$F$4),1)</f>
-        <v>39.299999999999997</v>
+        <v>50.7</v>
       </c>
       <c r="H13" s="13">
         <f t="shared" si="1"/>
-        <v>78.7</v>
+        <v>101.3</v>
       </c>
       <c r="K13" s="26">
         <f t="shared" si="2"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>7</v>
       </c>
@@ -11619,22 +11619,22 @@
       </c>
       <c r="F14" s="17">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G14" s="17">
         <f>ROUND($C$4*(1-7/$F$4),1)</f>
-        <v>26.2</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="H14" s="17">
         <f t="shared" si="1"/>
-        <v>91.8</v>
+        <v>118.2</v>
       </c>
       <c r="K14" s="26">
         <f t="shared" si="2"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>8</v>
       </c>
@@ -11651,22 +11651,22 @@
       </c>
       <c r="F15" s="13">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G15" s="13">
         <f>ROUND($C$4*(1-8/$F$4),1)</f>
-        <v>13.1</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="1"/>
-        <v>104.9</v>
+        <v>135.1</v>
       </c>
       <c r="K15" s="26">
         <f t="shared" si="2"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>9</v>
       </c>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="F16" s="17">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G16" s="17">
         <f>ROUND($C$4*(1-9/$F$4),1)</f>
@@ -11691,14 +11691,14 @@
       </c>
       <c r="H16" s="17">
         <f t="shared" si="1"/>
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="K16" s="26">
         <f t="shared" si="2"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19"/>
       <c r="B17" s="19"/>
       <c r="C17" s="19" t="s">
@@ -11713,12 +11713,12 @@
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40" t="s">
         <v>20</v>
       </c>
@@ -11728,17 +11728,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="34"/>
       <c r="C21" s="29">
         <f>$F$16</f>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>31</v>
       </c>
@@ -11748,7 +11748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40" t="s">
         <v>83</v>
       </c>
@@ -11758,7 +11758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
         <v>84</v>
       </c>
@@ -11768,8 +11768,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="39" t="s">
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="35" t="s">
         <v>85</v>
       </c>
       <c r="B26" s="34"/>
@@ -11780,7 +11780,7 @@
       <c r="G26" s="34"/>
       <c r="H26" s="34"/>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="34"/>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -11792,16 +11792,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A26:H27"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -11818,7 +11818,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -11832,8 +11832,8 @@
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="34"/>
@@ -11844,8 +11844,8 @@
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>93</v>
       </c>
       <c r="B2" s="34"/>
@@ -11856,7 +11856,7 @@
       <c r="G2" s="34"/>
       <c r="H2" s="34"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>65</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>67</v>
       </c>
@@ -11901,7 +11901,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>0</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>1</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>2</v>
       </c>
@@ -11997,7 +11997,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>3</v>
       </c>
@@ -12029,7 +12029,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>4</v>
       </c>
@@ -12061,7 +12061,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
@@ -12093,7 +12093,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>6</v>
       </c>
@@ -12125,7 +12125,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>7</v>
       </c>
@@ -12157,7 +12157,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>8</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>9</v>
       </c>
@@ -12221,7 +12221,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>10</v>
       </c>
@@ -12253,7 +12253,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19" t="s">
@@ -12268,12 +12268,12 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
         <v>20</v>
       </c>
@@ -12283,7 +12283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>21</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40" t="s">
         <v>31</v>
       </c>
@@ -12303,7 +12303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
         <v>83</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="40" t="s">
         <v>84</v>
       </c>
@@ -12323,8 +12323,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="39" t="s">
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="35" t="s">
         <v>85</v>
       </c>
       <c r="B27" s="34"/>
@@ -12335,7 +12335,7 @@
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -12347,16 +12347,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:H28"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -12373,7 +12373,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -12387,8 +12387,8 @@
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>94</v>
       </c>
       <c r="B1" s="34"/>
@@ -12399,8 +12399,8 @@
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>95</v>
       </c>
       <c r="B2" s="34"/>
@@ -12411,7 +12411,7 @@
       <c r="G2" s="34"/>
       <c r="H2" s="34"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>65</v>
       </c>
@@ -12427,7 +12427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>67</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>0</v>
       </c>
@@ -12488,7 +12488,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>1</v>
       </c>
@@ -12520,7 +12520,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>2</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>3</v>
       </c>
@@ -12584,7 +12584,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>4</v>
       </c>
@@ -12616,7 +12616,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
@@ -12648,7 +12648,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>6</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>7</v>
       </c>
@@ -12712,7 +12712,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>8</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>9</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>10</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19" t="s">
@@ -12823,12 +12823,12 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
         <v>20</v>
       </c>
@@ -12838,7 +12838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>21</v>
       </c>
@@ -12848,7 +12848,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40" t="s">
         <v>31</v>
       </c>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
         <v>83</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="40" t="s">
         <v>84</v>
       </c>
@@ -12878,8 +12878,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="39" t="s">
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="35" t="s">
         <v>85</v>
       </c>
       <c r="B27" s="34"/>
@@ -12890,7 +12890,7 @@
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -12902,16 +12902,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:H28"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -12928,7 +12928,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -12942,8 +12942,8 @@
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>96</v>
       </c>
       <c r="B1" s="34"/>
@@ -12954,8 +12954,8 @@
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>97</v>
       </c>
       <c r="B2" s="34"/>
@@ -12966,7 +12966,7 @@
       <c r="G2" s="34"/>
       <c r="H2" s="34"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>65</v>
       </c>
@@ -12982,7 +12982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>67</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>0</v>
       </c>
@@ -13043,7 +13043,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>1</v>
       </c>
@@ -13075,7 +13075,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>2</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>3</v>
       </c>
@@ -13139,7 +13139,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>4</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>5</v>
       </c>
@@ -13203,7 +13203,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>6</v>
       </c>
@@ -13235,7 +13235,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>7</v>
       </c>
@@ -13267,7 +13267,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>8</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>9</v>
       </c>
@@ -13331,7 +13331,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>10</v>
       </c>
@@ -13363,7 +13363,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19" t="s">
@@ -13378,12 +13378,12 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
         <v>20</v>
       </c>
@@ -13393,7 +13393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>21</v>
       </c>
@@ -13403,7 +13403,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40" t="s">
         <v>31</v>
       </c>
@@ -13413,7 +13413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
         <v>83</v>
       </c>
@@ -13423,7 +13423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="40" t="s">
         <v>84</v>
       </c>
@@ -13433,8 +13433,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="39" t="s">
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="35" t="s">
         <v>85</v>
       </c>
       <c r="B27" s="34"/>
@@ -13445,7 +13445,7 @@
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -13457,16 +13457,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:H28"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -13483,7 +13483,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -13496,8 +13496,8 @@
     <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>98</v>
       </c>
       <c r="B1" s="34"/>
@@ -13508,8 +13508,8 @@
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>99</v>
       </c>
       <c r="B2" s="34"/>
@@ -13520,7 +13520,7 @@
       <c r="G2" s="34"/>
       <c r="H2" s="34"/>
     </row>
-    <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>26</v>
       </c>
@@ -13552,7 +13552,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>105</v>
       </c>
@@ -13583,7 +13583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>35</v>
       </c>
@@ -13655,7 +13655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
@@ -13691,7 +13691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>39</v>
       </c>
@@ -13727,7 +13727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>41</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>43</v>
       </c>
@@ -13799,7 +13799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>45</v>
       </c>
@@ -13817,8 +13817,8 @@
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="39" t="s">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
         <v>107</v>
       </c>
       <c r="B14" s="34"/>
@@ -13829,7 +13829,7 @@
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>

--- a/Fase 2/SIGMA_Burndown_Burnup.xlsx
+++ b/Fase 2/SIGMA_Burndown_Burnup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\SIGMA\Fase 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9725D6-50AF-4EA9-BC2D-FA974C5D2531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1E2014-3556-455C-8DB2-3D632D139FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
     <t>Alcance total</t>
   </si>
   <si>
-    <t>751 puntos · 132 historias · 20 épicas</t>
+    <t>785 puntos · 138 historias · 20 épicas</t>
   </si>
   <si>
     <t>Versión</t>
@@ -222,7 +222,7 @@
     <t>Release burnup</t>
   </si>
   <si>
-    <t>Puntos completados acumulados del proyecto contra los 751 puntos del alcance total.</t>
+    <t>Puntos completados acumulados del proyecto contra los 785 puntos del alcance total.</t>
   </si>
   <si>
     <t>Permite proyectar la fecha de término: si la pendiente de la línea de completado se mantiene, el punto donde alcanzaría la línea de alcance es la fecha realista de cierre.</t>
@@ -662,11 +662,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -946,7 +946,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B132-4762-B645-021A0F2657D1}"/>
+              <c16:uniqueId val="{00000000-B669-456A-9406-2265433BAD67}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1105,7 +1105,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B132-4762-B645-021A0F2657D1}"/>
+              <c16:uniqueId val="{00000001-B669-456A-9406-2265433BAD67}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1546,7 +1546,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EC1D-4FCC-8371-492022CFF2E3}"/>
+              <c16:uniqueId val="{00000000-E653-4D0B-8E1B-EEB9338F38D3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1696,7 +1696,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EC1D-4FCC-8371-492022CFF2E3}"/>
+              <c16:uniqueId val="{00000001-E653-4D0B-8E1B-EEB9338F38D3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2128,7 +2128,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FEEB-40E5-9A79-4E20A3027062}"/>
+              <c16:uniqueId val="{00000000-6CD0-479C-AE59-91C8F896EEE7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2287,7 +2287,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FEEB-40E5-9A79-4E20A3027062}"/>
+              <c16:uniqueId val="{00000001-6CD0-479C-AE59-91C8F896EEE7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2728,7 +2728,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-166E-4F7D-9AFC-5722D9B2A42E}"/>
+              <c16:uniqueId val="{00000000-6DB3-4853-9621-C4623ED6620E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2878,7 +2878,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-166E-4F7D-9AFC-5722D9B2A42E}"/>
+              <c16:uniqueId val="{00000001-6DB3-4853-9621-C4623ED6620E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3259,13 +3259,13 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>670</c:v>
+                  <c:v>704</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>561</c:v>
+                  <c:v>595</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>443</c:v>
@@ -3285,7 +3285,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8FEB-43CE-BD95-2FDECDAB0C88}"/>
+              <c16:uniqueId val="{00000000-92A3-4581-A3FE-1CF741DA5207}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3393,25 +3393,25 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3419,7 +3419,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8FEB-43CE-BD95-2FDECDAB0C88}"/>
+              <c16:uniqueId val="{00000001-92A3-4581-A3FE-1CF741DA5207}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3834,7 +3834,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5BC3-4248-A6E2-7C7B08511935}"/>
+              <c16:uniqueId val="{00000000-7B4E-4327-9294-CE769A78592D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3933,25 +3933,25 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>751</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3959,7 +3959,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5BC3-4248-A6E2-7C7B08511935}"/>
+              <c16:uniqueId val="{00000001-7B4E-4327-9294-CE769A78592D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4401,7 +4401,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9D41-4760-BC7C-E2BCC26D4EB9}"/>
+              <c16:uniqueId val="{00000000-4756-4B40-BAE7-BDBBCC90FBEF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4551,7 +4551,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9D41-4760-BC7C-E2BCC26D4EB9}"/>
+              <c16:uniqueId val="{00000001-4756-4B40-BAE7-BDBBCC90FBEF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4977,7 +4977,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-172D-46DF-BB90-EFEEF28ECA74}"/>
+              <c16:uniqueId val="{00000000-1696-495A-A292-5B5EC59D1120}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5130,7 +5130,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-172D-46DF-BB90-EFEEF28ECA74}"/>
+              <c16:uniqueId val="{00000001-1696-495A-A292-5B5EC59D1120}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5565,7 +5565,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-91CC-401B-8B02-5B7B1E06DF15}"/>
+              <c16:uniqueId val="{00000000-A71D-46CD-A25D-1A2DA63B78D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5709,7 +5709,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-91CC-401B-8B02-5B7B1E06DF15}"/>
+              <c16:uniqueId val="{00000001-A71D-46CD-A25D-1A2DA63B78D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6135,7 +6135,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-90F3-45C0-86C9-8423F7431A84}"/>
+              <c16:uniqueId val="{00000000-38B5-4B13-8892-CDD8124B9A84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6288,7 +6288,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-90F3-45C0-86C9-8423F7431A84}"/>
+              <c16:uniqueId val="{00000001-38B5-4B13-8892-CDD8124B9A84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6723,7 +6723,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5F19-4FE3-B914-D00D105EF2E8}"/>
+              <c16:uniqueId val="{00000000-E684-4B85-9399-16C0555CAD73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6867,7 +6867,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5F19-4FE3-B914-D00D105EF2E8}"/>
+              <c16:uniqueId val="{00000001-E684-4B85-9399-16C0555CAD73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7299,7 +7299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8CAE-46D0-AE60-2209B4ACED66}"/>
+              <c16:uniqueId val="{00000000-25EE-4874-B7C9-ADCF44E5871A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7458,7 +7458,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8CAE-46D0-AE60-2209B4ACED66}"/>
+              <c16:uniqueId val="{00000001-25EE-4874-B7C9-ADCF44E5871A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7899,7 +7899,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F856-43EA-9790-3D37FCC22436}"/>
+              <c16:uniqueId val="{00000000-286F-40B1-AE87-C8422D694F32}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8049,7 +8049,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F856-43EA-9790-3D37FCC22436}"/>
+              <c16:uniqueId val="{00000001-286F-40B1-AE87-C8422D694F32}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8481,7 +8481,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4CEF-4B47-95A0-1B9E35DE508D}"/>
+              <c16:uniqueId val="{00000000-8ED3-48C1-92F4-2D36F04E19BB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8640,7 +8640,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4CEF-4B47-95A0-1B9E35DE508D}"/>
+              <c16:uniqueId val="{00000001-8ED3-48C1-92F4-2D36F04E19BB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9804,7 +9804,7 @@
     <row r="21" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="7">
         <f>Release!$E$12</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="C21" s="8">
         <f>SUM(Release!$F$6:$F$11)</f>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="D21" s="8">
         <f>$B$21-$C$21</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="E21" s="9">
         <f>IFERROR($C$21/$B$21,0)</f>
@@ -10194,7 +10194,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="34"/>
@@ -10206,7 +10206,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>64</v>
       </c>
       <c r="B2" s="34"/>
@@ -10712,7 +10712,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="42" t="s">
         <v>87</v>
       </c>
       <c r="B32" s="34"/>
@@ -10745,17 +10745,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A32:H34"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A27:H28"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -10787,7 +10787,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>88</v>
       </c>
       <c r="B1" s="34"/>
@@ -10799,7 +10799,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>89</v>
       </c>
       <c r="B2" s="34"/>
@@ -11269,16 +11269,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A26:H27"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A26:H27"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -11310,7 +11310,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="34"/>
@@ -11322,7 +11322,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>91</v>
       </c>
       <c r="B2" s="34"/>
@@ -11792,16 +11792,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A26:H27"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A26:H27"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -11833,7 +11833,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="34"/>
@@ -11845,7 +11845,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>93</v>
       </c>
       <c r="B2" s="34"/>
@@ -12347,16 +12347,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A27:H28"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -12388,7 +12388,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>94</v>
       </c>
       <c r="B1" s="34"/>
@@ -12400,7 +12400,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>95</v>
       </c>
       <c r="B2" s="34"/>
@@ -12902,16 +12902,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A27:H28"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -12943,7 +12943,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>96</v>
       </c>
       <c r="B1" s="34"/>
@@ -12955,7 +12955,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>97</v>
       </c>
       <c r="B2" s="34"/>
@@ -13457,16 +13457,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A27:H28"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -13497,7 +13497,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>98</v>
       </c>
       <c r="B1" s="34"/>
@@ -13509,7 +13509,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>99</v>
       </c>
       <c r="B2" s="34"/>
@@ -13568,15 +13568,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="11">
-        <f>751</f>
-        <v>751</v>
+        <f>785</f>
+        <v>785</v>
       </c>
       <c r="H5" s="11">
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="K5" s="26">
         <f t="shared" ref="K5:K11" si="0">$E$12</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="L5" s="26">
         <f>$F$5</f>
@@ -13605,14 +13605,14 @@
       </c>
       <c r="G6" s="13">
         <f>$H$5-SUM($F$5:$F6)</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="H6" s="13">
-        <v>670</v>
+        <v>704</v>
       </c>
       <c r="K6" s="26">
         <f t="shared" si="0"/>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="L6" s="26">
         <f t="shared" ref="L6:L11" si="1">$L5+$F6</f>
@@ -13641,14 +13641,14 @@
       </c>
       <c r="G7" s="17">
         <f>$H$5-SUM($F$5:$F7)</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="H7" s="17">
-        <v>561</v>
+        <v>595</v>
       </c>
       <c r="K7" s="26">
         <f t="shared" si="0"/>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="L7" s="26">
         <f t="shared" si="1"/>
@@ -13669,7 +13669,7 @@
         <v>46308</v>
       </c>
       <c r="E8" s="11">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="F8" s="13">
         <f>'Sprint 3'!$E$16</f>
@@ -13677,14 +13677,14 @@
       </c>
       <c r="G8" s="13">
         <f>$H$5-SUM($F$5:$F8)</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="H8" s="13">
         <v>443</v>
       </c>
       <c r="K8" s="26">
         <f t="shared" si="0"/>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="L8" s="26">
         <f t="shared" si="1"/>
@@ -13713,14 +13713,14 @@
       </c>
       <c r="G9" s="17">
         <f>$H$5-SUM($F$5:$F9)</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="H9" s="17">
         <v>295</v>
       </c>
       <c r="K9" s="26">
         <f t="shared" si="0"/>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="L9" s="26">
         <f t="shared" si="1"/>
@@ -13749,14 +13749,14 @@
       </c>
       <c r="G10" s="13">
         <f>$H$5-SUM($F$5:$F10)</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="H10" s="13">
         <v>147</v>
       </c>
       <c r="K10" s="26">
         <f t="shared" si="0"/>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="L10" s="26">
         <f t="shared" si="1"/>
@@ -13785,14 +13785,14 @@
       </c>
       <c r="G11" s="17">
         <f>$H$5-SUM($F$5:$F11)</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="H11" s="17">
         <v>0</v>
       </c>
       <c r="K11" s="26">
         <f t="shared" si="0"/>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="L11" s="26">
         <f t="shared" si="1"/>
@@ -13808,7 +13808,7 @@
       <c r="D12" s="19"/>
       <c r="E12" s="19">
         <f>SUM(E6:E11)</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="F12" s="21">
         <f>SUM(F6:F11)</f>
